--- a/api/templates/reason_for_testing_report/en.xlsx
+++ b/api/templates/reason_for_testing_report/en.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\maiki\.oh-my-zsh\aspect\api\templates\reason_for_testing_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\reason_for_testing_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F06F66C-30BC-4997-A916-BCFC23B8F024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5C612F5A-0FE5-46A2-A6EA-9F38A85E803F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,9 +45,6 @@
     <t>Results by Test Reason</t>
   </si>
   <si>
-    <t>State:</t>
-  </si>
-  <si>
     <t>&lt;States&gt;</t>
   </si>
   <si>
@@ -65,12 +61,15 @@
   </si>
   <si>
     <t>&lt;Table&gt;</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -196,8 +195,36 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -505,9 +532,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2326CEF1-61C4-4E50-B46A-2D4CFEBE03F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
@@ -521,18 +548,18 @@
     </row>
     <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -541,7 +568,7 @@
     </row>
     <row r="5" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1"/>
     </row>
@@ -556,10 +583,10 @@
     </row>
     <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
